--- a/examples/sample-sales-orders.xlsx
+++ b/examples/sample-sales-orders.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Online Store" sheetId="1" r:id="rId1"/>
-    <sheet name="Retail Branch" sheetId="2" r:id="rId2"/>
-    <sheet name="Wholesale" sheetId="3" r:id="rId3"/>
+    <sheet name="January" sheetId="1" r:id="rId1"/>
+    <sheet name="February" sheetId="2" r:id="rId2"/>
+    <sheet name="March" sheetId="3" r:id="rId3"/>
     <sheet name="Notes" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:K10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -410,7 +410,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Customer Orders - Online Store</v>
+        <v>Customer Orders - January 2026</v>
       </c>
     </row>
     <row r="4">
@@ -424,30 +424,27 @@
         <v>City</v>
       </c>
       <c r="D4" t="str">
+        <v>Channel</v>
+      </c>
+      <c r="E4" t="str">
         <v>Order Date</v>
       </c>
-      <c r="E4" t="str">
+      <c r="F4" t="str">
         <v>Qty</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
         <v>Unit Price (IDR)</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>Total Amount (IDR)</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Discount (%)</v>
       </c>
       <c r="I4" t="str">
         <v>Delivery Days</v>
       </c>
       <c r="J4" t="str">
-        <v>Weight (kg)</v>
+        <v>Payment Method</v>
       </c>
       <c r="K4" t="str">
-        <v>Payment Method</v>
-      </c>
-      <c r="L4" t="str">
         <v>Status</v>
       </c>
     </row>
@@ -461,31 +458,28 @@
       <c r="C5" t="str">
         <v>Jakarta</v>
       </c>
-      <c r="D5" s="1" t="d">
-        <v>2026-01-08T00:00:00.000Z</v>
-      </c>
-      <c r="E5">
+      <c r="D5" t="str">
+        <v>Online</v>
+      </c>
+      <c r="E5" s="1" t="d">
+        <v>2026-01-06T00:00:00.000Z</v>
+      </c>
+      <c r="F5">
         <v>3</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>450000</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>1350000</v>
-      </c>
-      <c r="H5">
-        <v>10</v>
       </c>
       <c r="I5">
         <v>3</v>
       </c>
-      <c r="J5">
-        <v>2.4</v>
+      <c r="J5" t="str">
+        <v>Bank Transfer</v>
       </c>
       <c r="K5" t="str">
-        <v>Bank Transfer</v>
-      </c>
-      <c r="L5" t="str">
         <v>Delivered</v>
       </c>
     </row>
@@ -499,31 +493,28 @@
       <c r="C6" t="str">
         <v>Bandung</v>
       </c>
-      <c r="D6" s="1" t="d">
-        <v>2026-01-15T00:00:00.000Z</v>
-      </c>
-      <c r="E6">
+      <c r="D6" t="str">
+        <v>Retail</v>
+      </c>
+      <c r="E6" s="1" t="d">
+        <v>2026-01-09T00:00:00.000Z</v>
+      </c>
+      <c r="F6">
         <v>1</v>
-      </c>
-      <c r="F6">
-        <v>1250000</v>
       </c>
       <c r="G6">
         <v>1250000</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>1250000</v>
       </c>
       <c r="I6">
         <v>4</v>
       </c>
-      <c r="J6">
-        <v>1.1</v>
+      <c r="J6" t="str">
+        <v>Credit Card</v>
       </c>
       <c r="K6" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="L6" t="str">
         <v>Delivered</v>
       </c>
     </row>
@@ -532,36 +523,33 @@
         <v>ORD-1003</v>
       </c>
       <c r="B7" t="str">
-        <v>Dewi Lestari</v>
+        <v>Toko Makmur Jaya</v>
       </c>
       <c r="C7" t="str">
-        <v>Surabaya</v>
-      </c>
-      <c r="D7" s="1" t="d">
-        <v>2026-01-23T00:00:00.000Z</v>
-      </c>
-      <c r="E7">
-        <v>5</v>
+        <v>Bekasi</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Wholesale</v>
+      </c>
+      <c r="E7" s="1" t="d">
+        <v>2026-01-14T00:00:00.000Z</v>
       </c>
       <c r="F7">
-        <v>320000</v>
+        <v>40</v>
       </c>
       <c r="G7">
-        <v>1600000</v>
+        <v>245000</v>
       </c>
       <c r="H7">
-        <v>15</v>
+        <v>9800000</v>
       </c>
       <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Bank Transfer</v>
       </c>
       <c r="K7" t="str">
-        <v>E-Wallet</v>
-      </c>
-      <c r="L7" t="str">
         <v>Delivered</v>
       </c>
     </row>
@@ -570,37 +558,34 @@
         <v>ORD-1004</v>
       </c>
       <c r="B8" t="str">
-        <v>Siti Rahayu</v>
+        <v>Dewi Lestari</v>
       </c>
       <c r="C8" t="str">
-        <v>Jakarta</v>
-      </c>
-      <c r="D8" s="1" t="d">
-        <v>2026-02-04T00:00:00.000Z</v>
-      </c>
-      <c r="E8">
-        <v>2</v>
+        <v>Surabaya</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Online</v>
+      </c>
+      <c r="E8" s="1" t="d">
+        <v>2026-01-20T00:00:00.000Z</v>
       </c>
       <c r="F8">
-        <v>450000</v>
+        <v>5</v>
       </c>
       <c r="G8">
-        <v>900000</v>
+        <v>320000</v>
       </c>
       <c r="H8">
-        <v>10</v>
+        <v>1600000</v>
       </c>
       <c r="I8">
-        <v>3</v>
-      </c>
-      <c r="J8">
-        <v>1.6</v>
+        <v>5</v>
+      </c>
+      <c r="J8" t="str">
+        <v>E-Wallet</v>
       </c>
       <c r="K8" t="str">
-        <v>Bank Transfer</v>
-      </c>
-      <c r="L8" t="str">
-        <v>Shipped</v>
+        <v>Delivered</v>
       </c>
     </row>
     <row r="9">
@@ -608,37 +593,34 @@
         <v>ORD-1005</v>
       </c>
       <c r="B9" t="str">
-        <v>Andi Pratama</v>
+        <v>Hendra Gunawan</v>
       </c>
       <c r="C9" t="str">
-        <v>Medan</v>
-      </c>
-      <c r="D9" s="1" t="d">
-        <v>2026-02-19T00:00:00.000Z</v>
-      </c>
-      <c r="E9">
-        <v>4</v>
+        <v>Semarang</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Retail</v>
+      </c>
+      <c r="E9" s="1" t="d">
+        <v>2026-01-23T00:00:00.000Z</v>
       </c>
       <c r="F9">
-        <v>275000</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>1100000</v>
+        <v>680000</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1360000</v>
       </c>
       <c r="I9">
-        <v>7</v>
-      </c>
-      <c r="J9">
-        <v>3.2</v>
+        <v>1</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Cash</v>
       </c>
       <c r="K9" t="str">
-        <v>COD</v>
-      </c>
-      <c r="L9" t="str">
-        <v>Shipped</v>
+        <v>Delivered</v>
       </c>
     </row>
     <row r="10">
@@ -646,80 +628,39 @@
         <v>ORD-1006</v>
       </c>
       <c r="B10" t="str">
-        <v>Dewi Lestari</v>
+        <v>Siti Rahayu</v>
       </c>
       <c r="C10" t="str">
-        <v>Surabaya</v>
-      </c>
-      <c r="D10" s="1" t="d">
-        <v>2026-03-02T00:00:00.000Z</v>
-      </c>
-      <c r="E10">
-        <v>6</v>
+        <v>Jakarta</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Online</v>
+      </c>
+      <c r="E10" s="1" t="d">
+        <v>2026-01-29T00:00:00.000Z</v>
       </c>
       <c r="F10">
-        <v>320000</v>
+        <v>2</v>
       </c>
       <c r="G10">
-        <v>1920000</v>
+        <v>450000</v>
       </c>
       <c r="H10">
-        <v>15</v>
+        <v>900000</v>
       </c>
       <c r="I10">
-        <v>5</v>
-      </c>
-      <c r="J10">
-        <v>4.8</v>
+        <v>3</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Bank Transfer</v>
       </c>
       <c r="K10" t="str">
-        <v>E-Wallet</v>
-      </c>
-      <c r="L10" t="str">
-        <v>Processing</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>ORD-1007</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Rina Wijaya</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Jakarta</v>
-      </c>
-      <c r="D11" s="1" t="d">
-        <v>2026-03-18T00:00:00.000Z</v>
-      </c>
-      <c r="E11">
-        <v>2</v>
-      </c>
-      <c r="F11">
-        <v>1250000</v>
-      </c>
-      <c r="G11">
-        <v>2500000</v>
-      </c>
-      <c r="H11">
-        <v>5</v>
-      </c>
-      <c r="I11">
-        <v>4</v>
-      </c>
-      <c r="J11">
-        <v>2.2</v>
-      </c>
-      <c r="K11" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="L11" t="str">
-        <v>Processing</v>
+        <v>Delivered</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K10"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -730,7 +671,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Customer Orders - Retail Branch</v>
+        <v>Customer Orders - February 2026</v>
       </c>
     </row>
     <row r="3">
@@ -744,25 +685,25 @@
         <v>City</v>
       </c>
       <c r="D3" t="str">
+        <v>Channel</v>
+      </c>
+      <c r="E3" t="str">
         <v>Order Date</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
         <v>Qty</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
         <v>Unit Price (IDR)</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v>Total Amount (IDR)</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
         <v>Discount (%)</v>
       </c>
-      <c r="I3" t="str">
+      <c r="J3" t="str">
         <v>Delivery Days</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Weight (kg)</v>
       </c>
       <c r="K3" t="str">
         <v>Payment Method</v>
@@ -773,37 +714,37 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ORD-2001</v>
+        <v>ORD-1007</v>
       </c>
       <c r="B4" t="str">
-        <v>Hendra Gunawan</v>
+        <v>Maya Putri</v>
       </c>
       <c r="C4" t="str">
-        <v>Semarang</v>
-      </c>
-      <c r="D4" s="1" t="d">
-        <v>2026-01-11T00:00:00.000Z</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
+        <v>Yogyakarta</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Retail</v>
+      </c>
+      <c r="E4" s="1" t="d">
+        <v>2026-02-03T00:00:00.000Z</v>
       </c>
       <c r="F4">
-        <v>680000</v>
+        <v>3</v>
       </c>
       <c r="G4">
-        <v>1360000</v>
+        <v>540000</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>1620000</v>
       </c>
       <c r="I4">
+        <v>12</v>
+      </c>
+      <c r="J4">
         <v>1</v>
       </c>
-      <c r="J4">
-        <v>1.8</v>
-      </c>
       <c r="K4" t="str">
-        <v>Cash</v>
+        <v>Debit Card</v>
       </c>
       <c r="L4" t="str">
         <v>Delivered</v>
@@ -811,37 +752,37 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ORD-2002</v>
+        <v>ORD-1008</v>
       </c>
       <c r="B5" t="str">
-        <v>Maya Putri</v>
+        <v>CV Sumber Rejeki</v>
       </c>
       <c r="C5" t="str">
-        <v>Yogyakarta</v>
-      </c>
-      <c r="D5" s="1" t="d">
-        <v>2026-01-29T00:00:00.000Z</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
+        <v>Tangerang</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Wholesale</v>
+      </c>
+      <c r="E5" s="1" t="d">
+        <v>2026-02-07T00:00:00.000Z</v>
       </c>
       <c r="F5">
-        <v>540000</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>1620000</v>
+        <v>250000</v>
       </c>
       <c r="H5">
-        <v>12</v>
+        <v>6250000</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J5">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="K5" t="str">
-        <v>Debit Card</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="L5" t="str">
         <v>Delivered</v>
@@ -849,37 +790,37 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ORD-2003</v>
+        <v>ORD-1009</v>
       </c>
       <c r="B6" t="str">
-        <v>Hendra Gunawan</v>
+        <v>Andi Pratama</v>
       </c>
       <c r="C6" t="str">
-        <v>Semarang</v>
-      </c>
-      <c r="D6" s="1" t="d">
-        <v>2026-02-13T00:00:00.000Z</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
+        <v>Medan</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Online</v>
+      </c>
+      <c r="E6" s="1" t="d">
+        <v>2026-02-12T00:00:00.000Z</v>
       </c>
       <c r="F6">
-        <v>680000</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>680000</v>
+        <v>275000</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>1100000</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>0.9</v>
+        <v>7</v>
       </c>
       <c r="K6" t="str">
-        <v>Cash</v>
+        <v>COD</v>
       </c>
       <c r="L6" t="str">
         <v>Delivered</v>
@@ -887,75 +828,75 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ORD-2004</v>
+        <v>ORD-1010</v>
       </c>
       <c r="B7" t="str">
-        <v>Tono Saputra</v>
+        <v>Hendra Gunawan</v>
       </c>
       <c r="C7" t="str">
-        <v>Solo</v>
-      </c>
-      <c r="D7" s="1" t="d">
-        <v>2026-02-27T00:00:00.000Z</v>
-      </c>
-      <c r="E7">
-        <v>4</v>
+        <v>Semarang</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Retail</v>
+      </c>
+      <c r="E7" s="1" t="d">
+        <v>2026-02-18T00:00:00.000Z</v>
       </c>
       <c r="F7">
-        <v>395000</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>1580000</v>
+        <v>680000</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>680000</v>
       </c>
       <c r="I7">
+        <v>8</v>
+      </c>
+      <c r="J7">
         <v>2</v>
       </c>
-      <c r="J7">
-        <v>3.6</v>
-      </c>
       <c r="K7" t="str">
-        <v>Debit Card</v>
+        <v>Cash</v>
       </c>
       <c r="L7" t="str">
-        <v>Shipped</v>
+        <v>Delivered</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ORD-2005</v>
+        <v>ORD-1011</v>
       </c>
       <c r="B8" t="str">
-        <v>Maya Putri</v>
+        <v>Dewi Lestari</v>
       </c>
       <c r="C8" t="str">
-        <v>Yogyakarta</v>
-      </c>
-      <c r="D8" s="1" t="d">
-        <v>2026-03-12T00:00:00.000Z</v>
-      </c>
-      <c r="E8">
-        <v>2</v>
+        <v>Surabaya</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Online</v>
+      </c>
+      <c r="E8" s="1" t="d">
+        <v>2026-02-24T00:00:00.000Z</v>
       </c>
       <c r="F8">
-        <v>540000</v>
+        <v>6</v>
       </c>
       <c r="G8">
-        <v>1080000</v>
+        <v>320000</v>
       </c>
       <c r="H8">
-        <v>12</v>
+        <v>1920000</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J8">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="K8" t="str">
-        <v>Cash</v>
+        <v>E-Wallet</v>
       </c>
       <c r="L8" t="str">
         <v>Shipped</v>
@@ -963,40 +904,40 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ORD-2006</v>
+        <v>ORD-1012</v>
       </c>
       <c r="B9" t="str">
-        <v>Lina Kusuma</v>
+        <v>Tono Saputra</v>
       </c>
       <c r="C9" t="str">
-        <v>Magelang</v>
-      </c>
-      <c r="D9" s="1" t="d">
-        <v>2026-03-26T00:00:00.000Z</v>
-      </c>
-      <c r="E9">
+        <v>Solo</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Retail</v>
+      </c>
+      <c r="E9" s="1" t="d">
+        <v>2026-02-27T00:00:00.000Z</v>
+      </c>
+      <c r="F9">
+        <v>4</v>
+      </c>
+      <c r="G9">
+        <v>395000</v>
+      </c>
+      <c r="H9">
+        <v>1580000</v>
+      </c>
+      <c r="I9">
         <v>5</v>
       </c>
-      <c r="F9">
-        <v>310000</v>
-      </c>
-      <c r="G9">
-        <v>1550000</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>3</v>
-      </c>
       <c r="J9">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="K9" t="str">
         <v>Debit Card</v>
       </c>
       <c r="L9" t="str">
-        <v>Processing</v>
+        <v>Shipped</v>
       </c>
     </row>
   </sheetData>
@@ -1008,7 +949,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1021,30 +962,36 @@
         <v>City</v>
       </c>
       <c r="D1" t="str">
+        <v>Channel</v>
+      </c>
+      <c r="E1" t="str">
         <v>Order Date</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Qty</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
+        <v>Unit Price (IDR)</v>
+      </c>
+      <c r="H1" t="str">
         <v>Total Amount (IDR)</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>Discount (%)</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>Delivery Days</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>Payment Method</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>Status</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ORD-3001</v>
+        <v>ORD-1013</v>
       </c>
       <c r="B2" t="str">
         <v>Toko Makmur Jaya</v>
@@ -1052,127 +999,189 @@
       <c r="C2" t="str">
         <v>Bekasi</v>
       </c>
-      <c r="D2" s="1" t="d">
-        <v>2026-01-20T00:00:00.000Z</v>
-      </c>
-      <c r="E2">
-        <v>40</v>
+      <c r="D2" t="str">
+        <v>Wholesale</v>
+      </c>
+      <c r="E2" s="1" t="d">
+        <v>2026-03-04T00:00:00.000Z</v>
       </c>
       <c r="F2">
-        <v>9800000</v>
+        <v>60</v>
       </c>
       <c r="G2">
-        <v>20</v>
+        <v>240000</v>
       </c>
       <c r="H2">
-        <v>6</v>
-      </c>
-      <c r="I2" t="str">
+        <v>14400000</v>
+      </c>
+      <c r="I2">
+        <v>22</v>
+      </c>
+      <c r="J2">
+        <v>8</v>
+      </c>
+      <c r="K2" t="str">
         <v>Bank Transfer</v>
       </c>
-      <c r="J2" t="str">
+      <c r="L2" t="str">
         <v>Delivered</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ORD-3002</v>
+        <v>ORD-1014</v>
       </c>
       <c r="B3" t="str">
-        <v>CV Sumber Rejeki</v>
+        <v>Rina Wijaya</v>
       </c>
       <c r="C3" t="str">
-        <v>Tangerang</v>
-      </c>
-      <c r="D3" s="1" t="d">
-        <v>2026-02-10T00:00:00.000Z</v>
-      </c>
-      <c r="E3">
-        <v>25</v>
+        <v>Jakarta</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Online</v>
+      </c>
+      <c r="E3" s="1" t="d">
+        <v>2026-03-10T00:00:00.000Z</v>
       </c>
       <c r="F3">
-        <v>6250000</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>18</v>
+        <v>1250000</v>
       </c>
       <c r="H3">
+        <v>2500000</v>
+      </c>
+      <c r="I3">
         <v>5</v>
       </c>
-      <c r="I3" t="str">
-        <v>Bank Transfer</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Delivered</v>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Credit Card</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Shipped</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ORD-3003</v>
+        <v>ORD-1015</v>
       </c>
       <c r="B4" t="str">
-        <v>Toko Makmur Jaya</v>
+        <v>Maya Putri</v>
       </c>
       <c r="C4" t="str">
-        <v>Bekasi</v>
-      </c>
-      <c r="D4" s="1" t="d">
-        <v>2026-03-05T00:00:00.000Z</v>
-      </c>
-      <c r="E4">
-        <v>60</v>
+        <v>Yogyakarta</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Retail</v>
+      </c>
+      <c r="E4" s="1" t="d">
+        <v>2026-03-16T00:00:00.000Z</v>
       </c>
       <c r="F4">
-        <v>14400000</v>
+        <v>2</v>
       </c>
       <c r="G4">
-        <v>22</v>
+        <v>540000</v>
       </c>
       <c r="H4">
-        <v>8</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Bank Transfer</v>
-      </c>
-      <c r="J4" t="str">
+        <v>1080000</v>
+      </c>
+      <c r="I4">
+        <v>12</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Cash</v>
+      </c>
+      <c r="L4" t="str">
         <v>Shipped</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ORD-3004</v>
+        <v>ORD-1016</v>
       </c>
       <c r="B5" t="str">
+        <v>Lina Kusuma</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Magelang</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Retail</v>
+      </c>
+      <c r="E5" s="1" t="d">
+        <v>2026-03-23T00:00:00.000Z</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>310000</v>
+      </c>
+      <c r="H5">
+        <v>1550000</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Debit Card</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Processing</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>ORD-1017</v>
+      </c>
+      <c r="B6" t="str">
         <v>UD Berkah Abadi</v>
       </c>
-      <c r="C5" t="str">
+      <c r="C6" t="str">
         <v>Depok</v>
       </c>
-      <c r="D5" s="1" t="d">
+      <c r="D6" t="str">
+        <v>Wholesale</v>
+      </c>
+      <c r="E6" s="1" t="d">
         <v>2026-03-30T00:00:00.000Z</v>
       </c>
-      <c r="E5">
+      <c r="F6">
         <v>30</v>
       </c>
-      <c r="F5">
+      <c r="G6">
+        <v>250000</v>
+      </c>
+      <c r="H6">
         <v>7500000</v>
       </c>
-      <c r="G5">
+      <c r="I6">
         <v>18</v>
       </c>
-      <c r="H5">
+      <c r="J6">
         <v>6</v>
       </c>
-      <c r="I5" t="str">
+      <c r="K6" t="str">
         <v>Bank Transfer</v>
       </c>
-      <c r="J5" t="str">
+      <c r="L6" t="str">
         <v>Processing</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1188,7 +1197,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>This tab is intentionally almost empty, to show that SheetSnap skips a sheet that has no data table instead of inventing numbers for it.</v>
+        <v>This tab is intentionally almost empty, to show that SheetSnap skips a sheet with no data table instead of inventing numbers for it.</v>
       </c>
     </row>
   </sheetData>
